--- a/output/roomself_excel/11589.xlsx
+++ b/output/roomself_excel/11589.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34816</v>
+        <v>159060</v>
       </c>
       <c r="D2" t="n">
-        <v>1540</v>
+        <v>3716</v>
       </c>
       <c r="E2" t="n">
-        <v>236</v>
+        <v>472</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58632</v>
+        <v>240726</v>
       </c>
       <c r="D3" t="n">
-        <v>2068</v>
+        <v>5768</v>
       </c>
       <c r="E3" t="n">
-        <v>375</v>
+        <v>598</v>
       </c>
       <c r="F3" t="n">
-        <v>223</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>474536</v>
+        <v>98647</v>
       </c>
       <c r="D4" t="n">
-        <v>9608</v>
+        <v>2696</v>
       </c>
       <c r="E4" t="n">
-        <v>1001</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98647</v>
+        <v>106902</v>
       </c>
       <c r="D5" t="n">
-        <v>2696</v>
+        <v>2876</v>
       </c>
       <c r="E5" t="n">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>106902</v>
+        <v>84500</v>
       </c>
       <c r="D6" t="n">
-        <v>2876</v>
+        <v>2352</v>
       </c>
       <c r="E6" t="n">
-        <v>854</v>
+        <v>386</v>
       </c>
       <c r="F6" t="n">
-        <v>353</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24480</v>
+        <v>27547</v>
       </c>
       <c r="D7" t="n">
-        <v>1252</v>
+        <v>1328</v>
       </c>
       <c r="E7" t="n">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="F7" t="n">
-        <v>190</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27547</v>
+        <v>16093</v>
       </c>
       <c r="D8" t="n">
-        <v>1328</v>
+        <v>1016</v>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85680</v>
+        <v>27873</v>
       </c>
       <c r="D9" t="n">
-        <v>3767</v>
+        <v>1336</v>
       </c>
       <c r="E9" t="n">
-        <v>854</v>
+        <v>171</v>
       </c>
       <c r="F9" t="n">
-        <v>695</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13034</v>
+        <v>85680</v>
       </c>
       <c r="D10" t="n">
-        <v>924</v>
+        <v>3767</v>
       </c>
       <c r="E10" t="n">
-        <v>133</v>
+        <v>468</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16093</v>
+        <v>74750</v>
       </c>
       <c r="D11" t="n">
-        <v>1016</v>
+        <v>2636</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27873</v>
+        <v>192820</v>
       </c>
       <c r="D12" t="n">
-        <v>1336</v>
+        <v>3728</v>
       </c>
       <c r="E12" t="n">
-        <v>171</v>
+        <v>504</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>84500</v>
+        <v>34816</v>
       </c>
       <c r="D13" t="n">
-        <v>2352</v>
+        <v>1540</v>
       </c>
       <c r="E13" t="n">
-        <v>543</v>
+        <v>236</v>
       </c>
       <c r="F13" t="n">
-        <v>386</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>192820</v>
+        <v>13034</v>
       </c>
       <c r="D14" t="n">
-        <v>3728</v>
+        <v>924</v>
       </c>
       <c r="E14" t="n">
-        <v>854</v>
+        <v>133</v>
       </c>
       <c r="F14" t="n">
-        <v>449</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>58632</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2068</v>
+      </c>
+      <c r="E15" t="n">
+        <v>168</v>
+      </c>
+      <c r="F15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24480</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1252</v>
+      </c>
+      <c r="E16" t="n">
+        <v>204</v>
+      </c>
+      <c r="F16" t="n">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11589.xlsx
+++ b/output/roomself_excel/11589.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3716</v>
       </c>
-      <c r="E2" t="n">
-        <v>472</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>403</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>359</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +551,38 @@
       <c r="D3" t="n">
         <v>5768</v>
       </c>
-      <c r="E3" t="n">
-        <v>598</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>505</v>
+        <v>552</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>219</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>437</v>
+      </c>
+      <c r="M3" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +600,31 @@
       <c r="D4" t="n">
         <v>2696</v>
       </c>
-      <c r="E4" t="n">
-        <v>400</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>291</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>253</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +641,31 @@
       <c r="D5" t="n">
         <v>2876</v>
       </c>
-      <c r="E5" t="n">
-        <v>441</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>353</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="G5" t="n">
+        <v>38</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>315</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +682,31 @@
       <c r="D6" t="n">
         <v>2352</v>
       </c>
-      <c r="E6" t="n">
-        <v>386</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>286</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>314</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +723,23 @@
       <c r="D7" t="n">
         <v>1328</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>169</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>34</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +756,15 @@
       <c r="D8" t="n">
         <v>1016</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +781,23 @@
       <c r="D9" t="n">
         <v>1336</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>171</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>34</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +814,23 @@
       <c r="D10" t="n">
         <v>3767</v>
       </c>
-      <c r="E10" t="n">
-        <v>468</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>177</v>
       </c>
+      <c r="G10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +847,31 @@
       <c r="D11" t="n">
         <v>2636</v>
       </c>
-      <c r="E11" t="n">
-        <v>352</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>159</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G11" t="n">
+        <v>34</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>318</v>
+      </c>
+      <c r="J11" t="n">
+        <v>33</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +888,31 @@
       <c r="D12" t="n">
         <v>3728</v>
       </c>
-      <c r="E12" t="n">
-        <v>504</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>449</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="G12" t="n">
+        <v>37</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>430</v>
+      </c>
+      <c r="J12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +929,23 @@
       <c r="D13" t="n">
         <v>1540</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>236</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>20</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +962,23 @@
       <c r="D14" t="n">
         <v>924</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>133</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>36</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +995,23 @@
       <c r="D15" t="n">
         <v>2068</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>168</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>37</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1028,31 @@
       <c r="D16" t="n">
         <v>1252</v>
       </c>
-      <c r="E16" t="n">
-        <v>204</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>190</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="G16" t="n">
+        <v>44</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>160</v>
+      </c>
+      <c r="J16" t="n">
+        <v>37</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
